--- a/exports/PERSISTENT_full_report.xlsx
+++ b/exports/PERSISTENT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.96</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.38541666666</v>
+        <v>44580.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>2150.1</v>
+        <v>2130</v>
       </c>
       <c r="I2" t="n">
         <v>2139.89553955</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.42</v>
+        <v>-5.31</v>
       </c>
       <c r="L2" t="n">
-        <v>5.25</v>
+        <v>6.84</v>
       </c>
       <c r="M2" t="n">
         <v>0.89</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.67</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44592.38541666666</v>
+        <v>44592.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>2193.05</v>
+        <v>2205</v>
       </c>
       <c r="I3" t="n">
         <v>2196.379676332821</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.96</v>
+        <v>-3.52</v>
       </c>
       <c r="L3" t="n">
         <v>5.61</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2100</v>
+        <v>2021.8</v>
       </c>
       <c r="I4" t="n">
         <v>2057.832360805049</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.76</v>
+        <v>-8.31</v>
       </c>
       <c r="L4" t="n">
-        <v>6.12</v>
+        <v>9.98</v>
       </c>
       <c r="M4" t="n">
-        <v>2.17</v>
+        <v>5.48</v>
       </c>
       <c r="N4" t="n">
-        <v>4.55</v>
+        <v>5.62</v>
       </c>
       <c r="O4" t="n">
         <v>2.97</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44628.38541666666</v>
+        <v>44628.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>2088.3</v>
+        <v>2107</v>
       </c>
       <c r="I5" t="n">
         <v>2089.607972983873</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.29</v>
+        <v>-4.21</v>
       </c>
       <c r="L5" t="n">
         <v>4.36</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44659.55208333334</v>
+        <v>44662.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2348.5</v>
+        <v>2274.9</v>
       </c>
       <c r="I6" t="n">
         <v>2327.414470710333</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K6" t="n">
-        <v>11.46</v>
+        <v>7.97</v>
       </c>
       <c r="L6" t="n">
         <v>1.36</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.8</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44679.38541666666</v>
+        <v>44679.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>2118.65</v>
+        <v>2149</v>
       </c>
       <c r="I7" t="n">
         <v>2131.815432323524</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>6.87</v>
+        <v>5.53</v>
       </c>
       <c r="L7" t="n">
         <v>3.3</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.83</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44691.38541666666</v>
+        <v>44691.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>2006.5</v>
+        <v>1973.5</v>
       </c>
       <c r="I8" t="n">
         <v>1985.369914852536</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.63</v>
+        <v>-8.17</v>
       </c>
       <c r="L8" t="n">
         <v>9.57</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.07</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44714.55208333334</v>
+        <v>44715.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1887.8</v>
+        <v>1916.8</v>
       </c>
       <c r="I9" t="n">
         <v>1900.358922478587</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>4.34</v>
+        <v>2.87</v>
       </c>
       <c r="L9" t="n">
         <v>1.95</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>7.36</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44721.55208333334</v>
+        <v>44722.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1810</v>
+        <v>1749.95</v>
       </c>
       <c r="I10" t="n">
         <v>1775.794116047302</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.57</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>6.92</v>
+        <v>9.26</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>2.81</v>
+        <v>3.47</v>
       </c>
       <c r="O10" t="n">
         <v>0.57</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44735.38541666666</v>
+        <v>44735.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>1632.5</v>
+        <v>1699.7</v>
       </c>
       <c r="I11" t="n">
         <v>1698.568377000566</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>6.71</v>
+        <v>2.87</v>
       </c>
       <c r="L11" t="n">
         <v>2.25</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10.73</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44756.55208333334</v>
+        <v>44757.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1599</v>
+        <v>1564.7</v>
       </c>
       <c r="I12" t="n">
         <v>1594.963039574205</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.92</v>
+        <v>-7.94</v>
       </c>
       <c r="L12" t="n">
-        <v>8.23</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>2.35</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.41</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44761.55208333334</v>
+        <v>44762.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1665</v>
+        <v>1726.35</v>
       </c>
       <c r="I13" t="n">
         <v>1699.225313598685</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.41</v>
+        <v>-10.33</v>
       </c>
       <c r="L13" t="n">
-        <v>6.79</v>
+        <v>11.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0.89</v>
+        <v>2.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.34</v>
+        <v>5.38</v>
       </c>
       <c r="O13" t="n">
         <v>-1.6</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>8.98</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1715</v>
+        <v>1667.5</v>
       </c>
       <c r="I14" t="n">
         <v>1684.864280274644</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.66</v>
+        <v>-3.41</v>
       </c>
       <c r="L14" t="n">
-        <v>2.83</v>
+        <v>3.79</v>
       </c>
       <c r="M14" t="n">
         <v>-0</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.56</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44774.38541666666</v>
+        <v>44774.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1822.2</v>
+        <v>1831</v>
       </c>
       <c r="I15" t="n">
         <v>1824.178737176563</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.279999999999999</v>
+        <v>-9.81</v>
       </c>
       <c r="L15" t="n">
         <v>10</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>7.41</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1851.55</v>
+        <v>1795.3</v>
       </c>
       <c r="I16" t="n">
         <v>1827.784759405311</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>1.12</v>
+        <v>-1.95</v>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>2.51</v>
       </c>
       <c r="M16" t="n">
-        <v>0.41</v>
+        <v>2.78</v>
       </c>
       <c r="N16" t="n">
         <v>2.99</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1652.5</v>
+        <v>1766.7</v>
       </c>
       <c r="I17" t="n">
         <v>1673.927659406494</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K17" t="n">
-        <v>7.95</v>
+        <v>1.59</v>
       </c>
       <c r="L17" t="n">
         <v>2.85</v>
       </c>
       <c r="M17" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>7.32</v>
       </c>
       <c r="O17" t="n">
         <v>-1.65</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.35</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44901.55208333334</v>
+        <v>44902.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2063.5</v>
+        <v>2042</v>
       </c>
       <c r="I18" t="n">
         <v>2047.050738961894</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K18" t="n">
-        <v>16.8</v>
+        <v>15.58</v>
       </c>
       <c r="L18" t="n">
         <v>5.35</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.18</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44928.38541666666</v>
+        <v>44928.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>2002.35</v>
+        <v>2015</v>
       </c>
       <c r="I19" t="n">
         <v>2014.186859128843</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>1.94</v>
+        <v>1.32</v>
       </c>
       <c r="L19" t="n">
         <v>3.21</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.87</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44985.38541666666</v>
+        <v>44985.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>2400</v>
+        <v>2387.6</v>
       </c>
       <c r="I20" t="n">
         <v>2398.875403797577</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>56.83333333333334</v>
+        <v>57</v>
       </c>
       <c r="K20" t="n">
-        <v>19.11</v>
+        <v>18.49</v>
       </c>
       <c r="L20" t="n">
         <v>4.71</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.5</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2166.5</v>
+        <v>2225.3</v>
       </c>
       <c r="I21" t="n">
         <v>2215.585726429294</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>52</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K21" t="n">
-        <v>9.26</v>
+        <v>6.8</v>
       </c>
       <c r="L21" t="n">
         <v>3.66</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.76</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45082.55208333334</v>
+        <v>45083.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2600</v>
+        <v>2478.4</v>
       </c>
       <c r="I22" t="n">
         <v>2517.49787612774</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K22" t="n">
-        <v>16.84</v>
+        <v>11.37</v>
       </c>
       <c r="L22" t="n">
         <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="N22" t="n">
-        <v>1.65</v>
+        <v>4.13</v>
       </c>
       <c r="O22" t="n">
         <v>3.14</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.27</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45107.38541666666</v>
+        <v>45107.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>2487.3</v>
+        <v>2503.55</v>
       </c>
       <c r="I23" t="n">
         <v>2499.518870926904</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.36</v>
+        <v>-1.01</v>
       </c>
       <c r="L23" t="n">
         <v>2.85</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>4.68</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45114.55208333334</v>
+        <v>45117.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>2413.5</v>
+        <v>2375.6</v>
       </c>
       <c r="I24" t="n">
         <v>2386.316557089162</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.6</v>
+        <v>-5.11</v>
       </c>
       <c r="L24" t="n">
-        <v>4.08</v>
+        <v>5.63</v>
       </c>
       <c r="M24" t="n">
         <v>0.87</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>5.6</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45121.38541666666</v>
+        <v>45121.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>2439.7</v>
+        <v>2462.5</v>
       </c>
       <c r="I25" t="n">
         <v>2453.159341188622</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.7</v>
+        <v>-3.66</v>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>5.25</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45127.55208333334</v>
+        <v>45128.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>2527.5</v>
+        <v>2387.1</v>
       </c>
       <c r="I26" t="n">
         <v>2418.680191189329</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>2.64</v>
+        <v>-3.06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.93</v>
+        <v>3.13</v>
       </c>
       <c r="M26" t="n">
-        <v>-0</v>
+        <v>3.26</v>
       </c>
       <c r="N26" t="n">
-        <v>1.49</v>
+        <v>5.8</v>
       </c>
       <c r="O26" t="n">
         <v>3.23</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.69</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45148.55208333334</v>
+        <v>45149.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>2420.05</v>
+        <v>2461.1</v>
       </c>
       <c r="I27" t="n">
         <v>2448.67581061022</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.38</v>
+        <v>-3.1</v>
       </c>
       <c r="L27" t="n">
         <v>3.68</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.79</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45196.55208333334</v>
+        <v>45197.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>2916.5</v>
+        <v>2843.3</v>
       </c>
       <c r="I28" t="n">
         <v>2858.368694808173</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K28" t="n">
-        <v>18.5</v>
+        <v>15.53</v>
       </c>
       <c r="L28" t="n">
         <v>3.34</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.5</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45219.38541666666</v>
+        <v>45219.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>2937.5</v>
+        <v>2955</v>
       </c>
       <c r="I29" t="n">
         <v>2950.831352357262</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.31</v>
+        <v>-3.93</v>
       </c>
       <c r="L29" t="n">
         <v>4.61</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.78</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45345.55208333334</v>
+        <v>45348.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>4310</v>
+        <v>4158.2</v>
       </c>
       <c r="I30" t="n">
         <v>4217.504573849948</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>126</v>
+        <v>128.8333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>45.85</v>
+        <v>40.72</v>
       </c>
       <c r="L30" t="n">
         <v>3.89</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.22</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45427.55208333334</v>
+        <v>45428.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3470</v>
+        <v>3504</v>
       </c>
       <c r="I31" t="n">
         <v>3488.010492401097</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>80</v>
       </c>
       <c r="K31" t="n">
-        <v>16.55</v>
+        <v>15.73</v>
       </c>
       <c r="L31" t="n">
         <v>4.94</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.33</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>3648</v>
+        <v>3540.45</v>
       </c>
       <c r="I32" t="n">
         <v>3561.206981577604</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>4.11</v>
+        <v>1.04</v>
       </c>
       <c r="L32" t="n">
         <v>1.1</v>
       </c>
       <c r="M32" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="N32" t="n">
-        <v>1.91</v>
+        <v>3.51</v>
       </c>
       <c r="O32" t="n">
         <v>1.38</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.19</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45448.55208333334</v>
+        <v>45449.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>3572.25</v>
+        <v>3684.85</v>
       </c>
       <c r="I33" t="n">
         <v>3598.303811167041</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.9</v>
+        <v>-4.08</v>
       </c>
       <c r="L33" t="n">
-        <v>2.81</v>
+        <v>4.92</v>
       </c>
       <c r="M33" t="n">
         <v>3.1</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45492.38541666666</v>
+        <v>45492.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>4598.1</v>
+        <v>4572</v>
       </c>
       <c r="I34" t="n">
         <v>4589.769631675712</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K34" t="n">
-        <v>24.78</v>
+        <v>24.08</v>
       </c>
       <c r="L34" t="n">
         <v>1.98</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>8.15</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>4760.05</v>
+        <v>4865</v>
       </c>
       <c r="I35" t="n">
         <v>4792.64839056612</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>26</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.11</v>
+        <v>-6.41</v>
       </c>
       <c r="L35" t="n">
         <v>8.59</v>
       </c>
       <c r="M35" t="n">
-        <v>1.33</v>
+        <v>1.89</v>
       </c>
       <c r="N35" t="n">
         <v>4</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.58</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>5237</v>
+        <v>5122</v>
       </c>
       <c r="I36" t="n">
         <v>5222.692018147398</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K36" t="n">
-        <v>7.65</v>
+        <v>5.28</v>
       </c>
       <c r="L36" t="n">
         <v>0.95</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45576.38541666666</v>
+        <v>45576.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>5393.9</v>
+        <v>5472</v>
       </c>
       <c r="I37" t="n">
         <v>5454.935742761589</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.31</v>
+        <v>-6.83</v>
       </c>
       <c r="L37" t="n">
-        <v>5.48</v>
+        <v>7.19</v>
       </c>
       <c r="M37" t="n">
         <v>0.6899999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.67</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45586.38541666666</v>
+        <v>45586.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>5400.25</v>
+        <v>5256</v>
       </c>
       <c r="I38" t="n">
         <v>5308.595949040225</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.31</v>
+        <v>-3.95</v>
       </c>
       <c r="L38" t="n">
-        <v>1.49</v>
+        <v>4.88</v>
       </c>
       <c r="M38" t="n">
         <v>0.53</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>7.82</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45587.55208333334</v>
+        <v>45588.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>5181.65</v>
+        <v>5750.35</v>
       </c>
       <c r="I39" t="n">
         <v>5552.556287620842</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>1.41</v>
+        <v>-9.41</v>
       </c>
       <c r="L39" t="n">
-        <v>2.99</v>
+        <v>10.33</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>10.44</v>
       </c>
       <c r="O39" t="n">
         <v>-4.9</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45595.55208333334</v>
+        <v>45596.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>5615</v>
+        <v>5324.65</v>
       </c>
       <c r="I40" t="n">
         <v>5328.33866003175</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.35</v>
+        <v>-7.4</v>
       </c>
       <c r="L40" t="n">
         <v>9.66</v>
@@ -2721,7 +3200,7 @@
         <v>0.51</v>
       </c>
       <c r="N40" t="n">
-        <v>0.96</v>
+        <v>4.33</v>
       </c>
       <c r="O40" t="n">
         <v>10.44</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.32</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45602.38541666666</v>
+        <v>45602.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>5701.65</v>
+        <v>5745.8</v>
       </c>
       <c r="I41" t="n">
         <v>5742.991241836855</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.08</v>
+        <v>-7.91</v>
       </c>
       <c r="L41" t="n">
-        <v>7.28</v>
+        <v>7.91</v>
       </c>
       <c r="M41" t="n">
         <v>1.05</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45649.55208333334</v>
+        <v>45650.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>6400</v>
+        <v>6374.4</v>
       </c>
       <c r="I42" t="n">
         <v>6379.388981647574</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>11.39</v>
+        <v>10.94</v>
       </c>
       <c r="L42" t="n">
         <v>2.85</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>5.55</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45679.55208333334</v>
+        <v>45680.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>5660</v>
+        <v>6347.9</v>
       </c>
       <c r="I43" t="n">
         <v>6147.248752641436</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K43" t="n">
-        <v>11.21</v>
+        <v>0.42</v>
       </c>
       <c r="L43" t="n">
         <v>6.19</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3.21</v>
+        <v>10.78</v>
       </c>
       <c r="O43" t="n">
         <v>-0.92</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>14.97</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45700.38541666666</v>
+        <v>45700.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>5789.1</v>
+        <v>5707</v>
       </c>
       <c r="I44" t="n">
         <v>5765.766956323609</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-8.800000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="L44" t="n">
         <v>13.71</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.77</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45741.55208333334</v>
+        <v>45742.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>5550</v>
+        <v>5582.6</v>
       </c>
       <c r="I45" t="n">
         <v>5578.330922895825</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="L45" t="n">
         <v>4.6</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>5237.95</v>
+        <v>4800.65</v>
       </c>
       <c r="I46" t="n">
         <v>5208.616930023181</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.17</v>
+        <v>-14.01</v>
       </c>
       <c r="L46" t="n">
-        <v>7.04</v>
+        <v>14.27</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9</v>
+        <v>2.24</v>
       </c>
       <c r="N46" t="n">
-        <v>4.48</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="O46" t="n">
         <v>-1.08</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>14.56</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45769.55208333334</v>
+        <v>45770.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>4966</v>
+        <v>5236.5</v>
       </c>
       <c r="I47" t="n">
         <v>4999.66779452414</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.44</v>
+        <v>-9.08</v>
       </c>
       <c r="L47" t="n">
-        <v>7.17</v>
+        <v>9.33</v>
       </c>
       <c r="M47" t="n">
         <v>3.75</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.15</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45846.38541666666</v>
+        <v>45846.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>5946</v>
+        <v>5770</v>
       </c>
       <c r="I48" t="n">
         <v>5832.380142277518</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>76</v>
+        <v>76.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>13.55</v>
+        <v>10.19</v>
       </c>
       <c r="L48" t="n">
         <v>3.89</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.47</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45859.38541666666</v>
+        <v>45859.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>5698</v>
+        <v>5789.5</v>
       </c>
       <c r="I49" t="n">
         <v>5720.762591717189</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K49" t="n">
-        <v>1.25</v>
+        <v>-0.34</v>
       </c>
       <c r="L49" t="n">
         <v>3.11</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.8</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>5603</v>
+        <v>5216</v>
       </c>
       <c r="I50" t="n">
         <v>5523.597812216917</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.22</v>
+        <v>-9.91</v>
       </c>
       <c r="L50" t="n">
-        <v>3.83</v>
+        <v>12.15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.04</v>
+        <v>1.39</v>
       </c>
       <c r="N50" t="n">
-        <v>2.24</v>
+        <v>7.64</v>
       </c>
       <c r="O50" t="n">
         <v>4.23</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.69</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>5250.5</v>
+        <v>5363.5</v>
       </c>
       <c r="I51" t="n">
         <v>5338.828324503739</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.66</v>
+        <v>-2.83</v>
       </c>
       <c r="L51" t="n">
         <v>5.92</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.98</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45904.55208333334</v>
+        <v>45905.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>5275</v>
+        <v>5112</v>
       </c>
       <c r="I52" t="n">
         <v>5219.731626413064</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.65</v>
+        <v>-4.69</v>
       </c>
       <c r="L52" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="M52" t="n">
         <v>0.96</v>
       </c>
       <c r="N52" t="n">
-        <v>1.84</v>
+        <v>2.67</v>
       </c>
       <c r="O52" t="n">
         <v>1.75</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.48</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>5130.5</v>
+        <v>5391.5</v>
       </c>
       <c r="I53" t="n">
         <v>5307.728771760514</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.36</v>
+        <v>-5.47</v>
       </c>
       <c r="L53" t="n">
-        <v>4.31</v>
+        <v>5.61</v>
       </c>
       <c r="M53" t="n">
         <v>0.47</v>
       </c>
       <c r="N53" t="n">
-        <v>2.22</v>
+        <v>5.45</v>
       </c>
       <c r="O53" t="n">
         <v>-2.67</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.08</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45922.38541666666</v>
+        <v>45922.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>5301.5</v>
+        <v>5269</v>
       </c>
       <c r="I54" t="n">
         <v>5299.391828214893</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.67</v>
+        <v>-2.27</v>
       </c>
       <c r="L54" t="n">
         <v>4.47</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.59</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>5069.2</v>
+        <v>5185</v>
       </c>
       <c r="I55" t="n">
         <v>5080.467103559715</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>3.79</v>
+        <v>1.59</v>
       </c>
       <c r="L55" t="n">
         <v>0.93</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.12</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46000.55208333334</v>
+        <v>46001.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>6310</v>
+        <v>6140.5</v>
       </c>
       <c r="I56" t="n">
         <v>6265.855653614277</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>64.16666666666667</v>
+        <v>65</v>
       </c>
       <c r="K56" t="n">
-        <v>21.7</v>
+        <v>18.43</v>
       </c>
       <c r="L56" t="n">
         <v>1.83</v>
@@ -3633,7 +4304,7 @@
         <v>1.41</v>
       </c>
       <c r="N56" t="n">
-        <v>2.74</v>
+        <v>4.15</v>
       </c>
       <c r="O56" t="n">
         <v>2.26</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.2</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>6365.5</v>
+        <v>6541.5</v>
       </c>
       <c r="I57" t="n">
         <v>6410.311398337575</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.66</v>
+        <v>-6.53</v>
       </c>
       <c r="L57" t="n">
-        <v>4.5</v>
+        <v>7.41</v>
       </c>
       <c r="M57" t="n">
         <v>0.95</v>
       </c>
       <c r="N57" t="n">
-        <v>2.93</v>
+        <v>3.21</v>
       </c>
       <c r="O57" t="n">
         <v>-4.15</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>5.83</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46017.55208333334</v>
+        <v>46020.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>6302</v>
+        <v>6246</v>
       </c>
       <c r="I58" t="n">
         <v>6260.366546063044</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.66</v>
+        <v>-4.52</v>
       </c>
       <c r="L58" t="n">
-        <v>4.07</v>
+        <v>5.11</v>
       </c>
       <c r="M58" t="n">
-        <v>-0</v>
+        <v>0.03</v>
       </c>
       <c r="N58" t="n">
         <v>1.85</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46028.55208333334</v>
+        <v>46029.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>6242.5</v>
+        <v>6508.5</v>
       </c>
       <c r="I59" t="n">
         <v>6460.100441644765</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K59" t="n">
-        <v>0.06</v>
+        <v>-4.2</v>
       </c>
       <c r="L59" t="n">
-        <v>1.33</v>
+        <v>4.39</v>
       </c>
       <c r="M59" t="n">
         <v>0.45</v>
       </c>
       <c r="N59" t="n">
-        <v>0.87</v>
+        <v>4.47</v>
       </c>
       <c r="O59" t="n">
         <v>-0.99</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.39</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46045.38541666666</v>
+        <v>46045.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>6195.5</v>
+        <v>6108</v>
       </c>
       <c r="I60" t="n">
         <v>6184.752618724228</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.81</v>
+        <v>-6.15</v>
       </c>
       <c r="L60" t="n">
         <v>7.39</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.96</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46111.55208333334</v>
+        <v>46113.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>4850</v>
+        <v>5096</v>
       </c>
       <c r="I61" t="n">
         <v>4954.628829267037</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>66</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>20.6</v>
+        <v>16.57</v>
       </c>
       <c r="L61" t="n">
         <v>7.28</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.82</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46133.55208333334</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>5369</v>
+        <v>5059.5</v>
       </c>
       <c r="I62" t="n">
         <v>5185.554789386659</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K62" t="n">
-        <v>5.36</v>
+        <v>-0.72</v>
       </c>
       <c r="L62" t="n">
         <v>3.4</v>
       </c>
       <c r="M62" t="n">
-        <v>1.94</v>
+        <v>2.82</v>
       </c>
       <c r="N62" t="n">
-        <v>2.26</v>
+        <v>5.57</v>
       </c>
       <c r="O62" t="n">
         <v>4.23</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.31</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46149.55208333334</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>4989.5</v>
+        <v>5111.9</v>
       </c>
       <c r="I63" t="n">
         <v>5037.359606132371</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K63" t="n">
-        <v>1.38</v>
+        <v>-1.04</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>7.22</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46155.55208333334</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>4848.2</v>
+        <v>4617.7</v>
       </c>
       <c r="I64" t="n">
         <v>4845.4345309507</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.16</v>
+        <v>-9.67</v>
       </c>
       <c r="L64" t="n">
-        <v>5.79</v>
+        <v>10.46</v>
       </c>
       <c r="M64" t="n">
         <v>0.8</v>
       </c>
       <c r="N64" t="n">
-        <v>4.04</v>
+        <v>4.54</v>
       </c>
       <c r="O64" t="n">
         <v>2.52</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>9.33</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46160.55208333334</v>
+        <v>46161.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>4960</v>
+        <v>5118.7</v>
       </c>
       <c r="I65" t="n">
         <v>4991.830120138326</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.41</v>
+        <v>-10.85</v>
       </c>
       <c r="L65" t="n">
-        <v>7.8</v>
+        <v>12.34</v>
       </c>
       <c r="M65" t="n">
         <v>0.11</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46176.38541666666</v>
+        <v>46176.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>5131</v>
+        <v>5087</v>
       </c>
       <c r="I66" t="n">
         <v>5124.634415306645</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>0.24</v>
+        <v>-0.62</v>
       </c>
       <c r="L66" t="n">
         <v>3.78</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.92</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>4587</v>
+        <v>4718</v>
       </c>
       <c r="I67" t="n">
         <v>4672.843876021901</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>9.83</v>
+        <v>7.25</v>
       </c>
       <c r="L67" t="n">
         <v>2.88</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>5871.5</v>
+        <v>5605</v>
       </c>
       <c r="I68" t="n">
         <v>5613.253798779055</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K68" t="n">
-        <v>24.45</v>
+        <v>18.8</v>
       </c>
       <c r="L68" t="n">
         <v>1.64</v>
@@ -4317,7 +5132,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>2.6</v>
+        <v>3.81</v>
       </c>
       <c r="O68" t="n">
         <v>1.92</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.97</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46296.55208333334</v>
+        <v>46300.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>5369.5</v>
+        <v>5532</v>
       </c>
       <c r="I69" t="n">
         <v>5497.964569913012</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>35</v>
       </c>
       <c r="K69" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="L69" t="n">
         <v>4.47</v>
@@ -4374,7 +5201,7 @@
         <v>2.04</v>
       </c>
       <c r="N69" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="O69" t="n">
         <v>-3.81</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4434,6 +5273,12 @@
       <c r="Q70" t="n">
         <v>32</v>
       </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6536,7 +7381,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="6">
@@ -6546,7 +7391,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="7">
@@ -6556,7 +7401,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="8">
@@ -6566,7 +7411,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -6576,7 +7421,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="10">
@@ -6586,7 +7431,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56.4</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="11">
@@ -6626,7 +7471,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.27</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="15">
@@ -6636,7 +7481,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.15</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="16">
@@ -6646,7 +7491,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="17">
@@ -6656,7 +7501,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45.85</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="18">
@@ -6666,7 +7511,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="19">
@@ -6676,7 +7521,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.47</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="20">
@@ -6686,7 +7531,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.94</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="21">
@@ -6696,7 +7541,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.71</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="22">
@@ -6706,7 +7551,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6716,7 +7561,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -6726,7 +7571,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="25">
@@ -6736,7 +7581,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.46</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="26">
@@ -6746,7 +7591,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.66</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="27">
@@ -6756,7 +7601,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.38</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="28">
@@ -6766,7 +7611,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
